--- a/data/trans_camb/P15-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P15-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,67</t>
+          <t>0,27; 4,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,81</t>
+          <t>-1,58; 2,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,14</t>
+          <t>-0,88; 3,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,49</t>
+          <t>0,25; 4,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,94</t>
+          <t>-0,68; 3,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,7</t>
+          <t>2,33; 6,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,85</t>
+          <t>0,9; 3,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,55</t>
+          <t>-0,36; 2,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,95</t>
+          <t>1,8; 4,88</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 103,89</t>
+          <t>3,5; 105,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 65,37</t>
+          <t>-25,82; 58,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 91,11</t>
+          <t>-13,62; 82,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,26; 82,98</t>
+          <t>3,23; 87,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 71,63</t>
+          <t>-9,91; 79,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,6; 128,14</t>
+          <t>30,21; 125,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,06; 76,81</t>
+          <t>14,31; 76,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 50,22</t>
+          <t>-6,22; 53,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,48; 95,9</t>
+          <t>27,79; 94,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,69</t>
+          <t>-1,32; 2,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; -0,97</t>
+          <t>-4,68; -0,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,25; -0,99</t>
+          <t>-5,27; -1,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,7</t>
+          <t>0,58; 3,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 1,11</t>
+          <t>-1,62; 1,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,42</t>
+          <t>-1,8; 1,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,67</t>
+          <t>0,03; 2,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,73; -0,42</t>
+          <t>-2,74; -0,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; -0,27</t>
+          <t>-3,1; -0,26</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 34,78</t>
+          <t>-13,43; 36,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,55; -12,72</t>
+          <t>-47,27; -11,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-55,32; -13,57</t>
+          <t>-55,27; -14,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 96,66</t>
+          <t>10,25; 96,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 30,71</t>
+          <t>-31,12; 31,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 35,79</t>
+          <t>-32,37; 37,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 44,23</t>
+          <t>0,37; 44,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,77; -7,09</t>
+          <t>-36,97; -7,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-40,11; -4,44</t>
+          <t>-41,33; -4,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 1,0</t>
+          <t>-5,13; 1,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 1,38</t>
+          <t>-4,89; 1,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 0,96</t>
+          <t>-5,2; 0,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 4,65</t>
+          <t>-1,51; 4,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 3,31</t>
+          <t>-2,44; 3,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,84</t>
+          <t>-2,61; 2,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,97</t>
+          <t>-2,7; 1,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,42</t>
+          <t>-2,72; 1,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,71</t>
+          <t>-3,51; 0,64</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-55,85; 21,23</t>
+          <t>-57,93; 20,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,64; 27,11</t>
+          <t>-55,36; 25,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-57,55; 19,59</t>
+          <t>-57,76; 14,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,5; 122,07</t>
+          <t>-24,63; 135,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,32; 93,1</t>
+          <t>-36,8; 92,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,87; 52,54</t>
+          <t>-38,67; 64,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,31; 39,18</t>
+          <t>-37,03; 38,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-36,59; 28,92</t>
+          <t>-36,75; 30,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-45,12; 14,77</t>
+          <t>-46,75; 12,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,36</t>
+          <t>-0,32; 2,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,73; -0,33</t>
+          <t>-2,78; -0,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,31; -0,31</t>
+          <t>-3,34; -0,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,24</t>
+          <t>0,97; 3,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,47</t>
+          <t>-0,9; 1,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,82</t>
+          <t>-0,68; 1,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,43</t>
+          <t>0,61; 2,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,19</t>
+          <t>-1,55; 0,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,49</t>
+          <t>-1,5; 0,45</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 35,39</t>
+          <t>-3,87; 34,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,78; -4,91</t>
+          <t>-34,5; -3,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,97; -4,62</t>
+          <t>-41,93; -4,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,7; 72,64</t>
+          <t>16,74; 72,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 31,65</t>
+          <t>-15,49; 29,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 38,63</t>
+          <t>-11,44; 36,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,26; 42,1</t>
+          <t>9,31; 41,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 3,5</t>
+          <t>-23,1; 2,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 8,17</t>
+          <t>-22,32; 7,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P15-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P15-Estudios-trans_camb.xlsx
@@ -634,22 +634,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>1,08</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,39</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,45</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,39</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,48</t>
+          <t>4,23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,27</t>
+          <t>2,95</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,83</t>
+          <t>0,09; 4,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,76</t>
+          <t>-1,52; 2,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,99</t>
+          <t>-1,15; 3,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 4,46</t>
+          <t>0,48; 4,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,94</t>
+          <t>-0,84; 3,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,56</t>
+          <t>2,18; 6,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,97</t>
+          <t>0,94; 3,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,74</t>
+          <t>-0,38; 2,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,88</t>
+          <t>1,39; 4,4</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>50,89%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 105,8</t>
+          <t>-0,03; 101,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 58,04</t>
+          <t>-25,88; 64,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 82,19</t>
+          <t>-18,7; 83,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 87,28</t>
+          <t>6,42; 86,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 79,13</t>
+          <t>-12,02; 71,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,21; 125,9</t>
+          <t>31,11; 124,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,31; 76,99</t>
+          <t>14,55; 78,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 53,15</t>
+          <t>-6,04; 51,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,79; 94,17</t>
+          <t>20,95; 83,91</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,92</t>
+          <t>-2,31</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,52</t>
+          <t>-0,94</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,75</t>
+          <t>-1,09; 2,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; -0,82</t>
+          <t>-4,47; -1,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,27; -1,04</t>
+          <t>-4,09; -0,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,75</t>
+          <t>0,42; 3,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,18</t>
+          <t>-1,69; 1,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,48</t>
+          <t>-0,87; 1,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,7</t>
+          <t>0,12; 2,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,74; -0,46</t>
+          <t>-2,79; -0,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; -0,26</t>
+          <t>-2,13; 0,24</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-33,98%</t>
+          <t>-26,9%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-0,19%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-22,92%</t>
+          <t>-14,14%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 36,06</t>
+          <t>-11,51; 33,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,27; -11,25</t>
+          <t>-46,34; -15,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-55,27; -14,29</t>
+          <t>-42,89; -7,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,25; 96,76</t>
+          <t>7,05; 92,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,12; 31,99</t>
+          <t>-32,34; 29,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 37,89</t>
+          <t>-16,09; 49,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 44,03</t>
+          <t>1,49; 45,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,97; -7,76</t>
+          <t>-36,9; -7,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-41,33; -4,14</t>
+          <t>-29,16; 3,71</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,31</t>
+          <t>-1,6</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,37</t>
+          <t>-0,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 1,13</t>
+          <t>-5,29; 1,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 1,4</t>
+          <t>-4,91; 1,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 0,78</t>
+          <t>-4,64; 1,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 4,48</t>
+          <t>-1,85; 4,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 3,45</t>
+          <t>-2,04; 3,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 2,04</t>
+          <t>-2,8; 2,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,97</t>
+          <t>-2,67; 1,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 1,52</t>
+          <t>-3,02; 1,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 0,64</t>
+          <t>-3,12; 0,95</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-31,05%</t>
+          <t>-21,43%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-4,72%</t>
+          <t>-2,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-21,82%</t>
+          <t>-15,22%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-57,93; 20,47</t>
+          <t>-57,21; 19,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,36; 25,73</t>
+          <t>-54,08; 23,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-57,76; 14,93</t>
+          <t>-50,7; 32,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 135,29</t>
+          <t>-29,01; 145,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,8; 92,57</t>
+          <t>-33,82; 106,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,67; 64,6</t>
+          <t>-40,81; 62,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-37,03; 38,55</t>
+          <t>-36,55; 37,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-36,75; 30,92</t>
+          <t>-40,0; 27,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-46,75; 12,74</t>
+          <t>-40,94; 18,34</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>-1,18</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-0,07</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,3</t>
+          <t>-0,31; 2,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; -0,28</t>
+          <t>-2,79; -0,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,34; -0,3</t>
+          <t>-2,48; 0,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,38</t>
+          <t>0,75; 3,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,37</t>
+          <t>-0,93; 1,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,7</t>
+          <t>-0,16; 2,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,39</t>
+          <t>0,68; 2,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,15</t>
+          <t>-1,48; 0,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,45</t>
+          <t>-0,86; 0,84</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-22,33%</t>
+          <t>-15,87%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-7,94%</t>
+          <t>-1,15%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 34,85</t>
+          <t>-3,84; 36,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,5; -3,98</t>
+          <t>-34,21; -3,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,93; -4,8</t>
+          <t>-31,42; 0,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,74; 72,6</t>
+          <t>12,84; 66,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 29,68</t>
+          <t>-16,47; 26,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 36,1</t>
+          <t>-2,8; 43,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,31; 41,13</t>
+          <t>9,83; 42,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 2,49</t>
+          <t>-21,85; 4,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 7,58</t>
+          <t>-12,64; 14,38</t>
         </is>
       </c>
     </row>
